--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487823_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487823_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5963</v>
+        <v>2.321</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4933</v>
+        <v>3.13</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.897</v>
+        <v>-0.8089</v>
       </c>
       <c r="G2" t="n">
         <v>2.7856</v>
@@ -610,13 +610,13 @@
         <v>0.4162</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3321</v>
+        <v>0.0568</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1553</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1866</v>
+        <v>-0.0985</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9376</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8399</v>
+        <v>1.4199</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6856</v>
+        <v>1.4094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1543</v>
+        <v>0.0105</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7455</v>
+        <v>-0.9495</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8018</v>
+        <v>-1.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9438</v>
+        <v>0.0825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0999</v>
+        <v>0.0467</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0176</v>
+        <v>-0.4929</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>0.5396</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8454</v>
+        <v>-0.9963</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7841</v>
+        <v>-0.5391</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0613</v>
+        <v>-0.4572</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.3705</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0548</v>
+        <v>-0.8387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1363</v>
+        <v>-0.3886</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0814</v>
+        <v>-0.4501</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8199</v>
+        <v>1.7513</v>
       </c>
       <c r="W3" t="n">
-        <v>5.8199</v>
+        <v>1.7513</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7704</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6152</v>
+        <v>1.3223</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1552</v>
+        <v>-0.3742</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0155</v>
+        <v>-1.7455</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2857</v>
+        <v>-0.8018</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2702</v>
+        <v>-0.9438</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0851</v>
+        <v>0.0999</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6819</v>
+        <v>-0.0176</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5968</v>
+        <v>0.1176</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0696</v>
+        <v>-1.8454</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3962</v>
+        <v>-0.7841</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3266</v>
+        <v>-1.0613</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0812</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.3299</v>
+        <v>-4.3705</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0223</v>
+        <v>-0.837</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4625</v>
+        <v>-0.2271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5598</v>
+        <v>-0.6099</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8137</v>
+        <v>5.8199</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>5.8199</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.8763</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7013</v>
+        <v>0.1028</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.107</v>
+        <v>0.7735</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9495</v>
+        <v>2.0155</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.032</v>
+        <v>2.2857</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0825</v>
+        <v>-0.2702</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0467</v>
+        <v>2.0851</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4929</v>
+        <v>2.6819</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5396</v>
+        <v>-0.5968</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9963</v>
+        <v>-0.0696</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5391</v>
+        <v>-0.3962</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4572</v>
+        <v>0.3266</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4568</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6643</v>
+        <v>0.1282</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0967</v>
+        <v>-0.05</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5675</v>
+        <v>0.1782</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7513</v>
+        <v>0.8137</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7513</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0345</v>
+        <v>0.2362</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3965</v>
+        <v>1.5689</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.362</v>
+        <v>-1.3326</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6369</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0986</v>
+        <v>-0.8969</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1833</v>
+        <v>-0.0109</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9153</v>
+        <v>-0.8859</v>
       </c>
       <c r="V6" t="n">
         <v>0.9376</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.443</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1682</v>
+        <v>-1.5316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7252</v>
+        <v>0.8426</v>
       </c>
       <c r="G7" t="n">
         <v>0.6032</v>
@@ -1000,13 +1000,13 @@
         <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8194</v>
+        <v>-1.0654</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0066</v>
+        <v>-0.37</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8128</v>
+        <v>-0.6954</v>
       </c>
       <c r="V7" t="n">
         <v>0.8137</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6387</v>
+        <v>-2.5125</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1667</v>
+        <v>-2.9524</v>
       </c>
       <c r="F8" t="n">
-        <v>0.528</v>
+        <v>0.4399</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5799</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.5164</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4443</v>
+        <v>-0.23</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1983</v>
+        <v>-0.2864</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0893</v>
+        <v>-3.8582</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4489</v>
+        <v>-3.2765</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6404</v>
+        <v>-0.5817</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4787</v>
@@ -1156,13 +1156,13 @@
         <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2995</v>
+        <v>-0.0683</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5219</v>
+        <v>-0.3495</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2225</v>
+        <v>0.2812</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1715</v>
+        <v>-4.4786</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1035</v>
+        <v>-2.6748</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.068</v>
+        <v>-1.8038</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3128</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5663</v>
+        <v>0.1266</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0443</v>
+        <v>0.2199</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8873</v>
+        <v>-7.0052</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2388</v>
+        <v>-5.6797</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6485</v>
+        <v>-1.3256</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7632</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6454</v>
+        <v>-0.7633</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1091</v>
+        <v>-0.55</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5362</v>
+        <v>-0.2133</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.3944</v>
+        <v>-12.742</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.234200000000001</v>
+        <v>-8.5816</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.160200000000001</v>
+        <v>-4.160299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-9.062200000000001</v>
@@ -1390,16 +1390,16 @@
         <v>10.4059</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3269</v>
+        <v>-4.674399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7664</v>
+        <v>-2.1141</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5601</v>
+        <v>-2.5602</v>
       </c>
       <c r="V12" t="n">
-        <v>8.278700000000001</v>
+        <v>8.278699999999999</v>
       </c>
       <c r="W12" t="n">
         <v>11.1799</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5067</v>
+        <v>4.6764</v>
       </c>
       <c r="E13" t="n">
-        <v>2.604</v>
+        <v>1.4252</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9027</v>
+        <v>3.2511</v>
       </c>
       <c r="G13" t="n">
         <v>1.2511</v>
@@ -1468,13 +1468,13 @@
         <v>2.7055</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5501</v>
+        <v>0.7197</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5526</v>
+        <v>0.3739</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0026</v>
+        <v>0.3458</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1519</v>
+        <v>4.6652</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0339</v>
+        <v>4.3277</v>
       </c>
       <c r="F14" t="n">
-        <v>1.118</v>
+        <v>0.3375</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8252</v>
+        <v>4.489</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1237</v>
+        <v>-1.1173</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7015</v>
+        <v>5.6064</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2825</v>
+        <v>4.1871</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2258</v>
+        <v>-1.2029</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0567</v>
+        <v>5.39</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4573</v>
+        <v>0.3019</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1022</v>
+        <v>0.0856</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3551</v>
+        <v>0.2164</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R14" t="n">
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5161</v>
+        <v>0.403</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2486</v>
+        <v>0.2405</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7647</v>
+        <v>0.1625</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.23</v>
+        <v>0.8137</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5667</v>
+        <v>4.0917</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5776</v>
+        <v>3.3554</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0109</v>
+        <v>0.7363</v>
       </c>
       <c r="G15" t="n">
-        <v>4.489</v>
+        <v>2.8252</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1173</v>
+        <v>0.1237</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6064</v>
+        <v>2.7015</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1871</v>
+        <v>3.2825</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2029</v>
+        <v>0.2258</v>
       </c>
       <c r="L15" t="n">
-        <v>5.39</v>
+        <v>3.0567</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3019</v>
+        <v>-0.4573</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0856</v>
+        <v>-0.1022</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2164</v>
+        <v>-0.3551</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0406</v>
+        <v>1.0406</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6955</v>
+        <v>0.4559</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1859</v>
+        <v>0.383</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8137</v>
+        <v>-0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5397</v>
+        <v>3.1</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3968</v>
+        <v>3.3219</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1429</v>
+        <v>-0.2219</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3954</v>
+        <v>3.2537</v>
       </c>
       <c r="H16" t="n">
-        <v>1.904</v>
+        <v>0.5375</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5086000000000001</v>
+        <v>2.7162</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8568</v>
+        <v>3.1886</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0104</v>
+        <v>0.403</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1535</v>
+        <v>2.7856</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4614</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1063</v>
+        <v>0.1346</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3551</v>
+        <v>-0.0694</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5637</v>
+        <v>0.3083</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5806</v>
+        <v>0.1334</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0169</v>
+        <v>0.1749</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4599</v>
+        <v>-2.3351</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3055</v>
+        <v>2.2579</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1541</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1514</v>
+        <v>1.2897</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3567</v>
+        <v>1.3954</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1022</v>
+        <v>1.904</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4588</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9896</v>
+        <v>1.8568</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9594</v>
+        <v>2.0104</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0302</v>
+        <v>-0.1535</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6329</v>
+        <v>-0.4614</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0616</v>
+        <v>-0.1063</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4286</v>
+        <v>-0.3551</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7407</v>
+        <v>0.2818</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2051</v>
+        <v>0.152</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5357</v>
+        <v>0.1299</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9912</v>
+        <v>0.8538</v>
       </c>
       <c r="E18" t="n">
-        <v>2.679</v>
+        <v>0.7611</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6878</v>
+        <v>0.0927</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2537</v>
+        <v>0.3567</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5375</v>
+        <v>-0.1022</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7162</v>
+        <v>0.4588</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1886</v>
+        <v>0.9896</v>
       </c>
       <c r="K18" t="n">
-        <v>0.403</v>
+        <v>0.9594</v>
       </c>
       <c r="L18" t="n">
-        <v>2.7856</v>
+        <v>0.0302</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.6329</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1346</v>
+        <v>-1.0616</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0694</v>
+        <v>0.4286</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8731</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8005</v>
+        <v>1.289</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.291</v>
+        <v>0.4769</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3351</v>
+        <v>-0.5838</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3351</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3769</v>
+        <v>0.8146</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.553</v>
+        <v>-1.2177</v>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>2.0324</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9066</v>
+        <v>0.4485</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2453</v>
+        <v>-1.0896</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6613</v>
+        <v>1.5381</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1679</v>
+        <v>0.759</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.028</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1959</v>
+        <v>1.5014</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7387</v>
+        <v>-0.3105</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2733</v>
+        <v>-0.3472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4654</v>
+        <v>0.0367</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8054</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3602</v>
+        <v>-0.2286</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4452</v>
+        <v>0.3054</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3351</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.141</v>
+        <v>0.3088</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9678</v>
+        <v>-1.0888</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8269</v>
+        <v>1.3976</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4485</v>
+        <v>0.9066</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0896</v>
+        <v>0.2453</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5381</v>
+        <v>0.6613</v>
       </c>
       <c r="J20" t="n">
-        <v>0.759</v>
+        <v>0.1679</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.028</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5014</v>
+        <v>0.1959</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3105</v>
+        <v>0.7387</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3472</v>
+        <v>0.2733</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0367</v>
+        <v>0.4654</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4974</v>
+        <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8788</v>
+        <v>1.7372</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9786</v>
+        <v>0.8244</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0998</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>-2.3351</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4599</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3088</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5069</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1982</v>
+        <v>1.4291</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3174</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2792</v>
+        <v>0.5102</v>
       </c>
       <c r="T21" t="n">
         <v>0.4005</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1213</v>
+        <v>0.1096</v>
       </c>
       <c r="V21" t="n">
         <v>0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7479</v>
+        <v>-2.974</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6687</v>
+        <v>-2.4544</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.5196</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1603</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4769</v>
+        <v>0.2509</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.3504</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1051</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8468</v>
+        <v>-3.6079</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5887</v>
+        <v>-3.7315</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2581</v>
+        <v>0.1236</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3864</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9786</v>
+        <v>-0.1214</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2518</v>
+        <v>0.1299</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8137</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.3941</v>
+        <v>14.1087</v>
       </c>
       <c r="E24" t="n">
-        <v>4.160300000000002</v>
+        <v>4.1602</v>
       </c>
       <c r="F24" t="n">
-        <v>9.234099999999998</v>
+        <v>9.948499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>9.062099999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1.428600000000001</v>
+        <v>1.4286</v>
       </c>
       <c r="I24" t="n">
         <v>7.633399999999999</v>
@@ -2305,10 +2305,10 @@
         <v>2.736900000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>6.367999999999997</v>
+        <v>6.367999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.04249999999999993</v>
+        <v>-0.04250000000000004</v>
       </c>
       <c r="N24" t="n">
         <v>-1.3081</v>
@@ -2326,16 +2326,16 @@
         <v>17.6901</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3268</v>
+        <v>6.0413</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5602</v>
+        <v>2.5601</v>
       </c>
       <c r="U24" t="n">
-        <v>2.766699999999999</v>
+        <v>3.4811</v>
       </c>
       <c r="V24" t="n">
-        <v>-8.2789</v>
+        <v>-8.278900000000002</v>
       </c>
       <c r="W24" t="n">
         <v>2.9012</v>
